--- a/FlyControl/Components/ICs_List/ICs_List.xlsx
+++ b/FlyControl/Components/ICs_List/ICs_List.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12180"/>
+    <workbookView windowWidth="28800" windowHeight="11580" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="OriginList" sheetId="1" r:id="rId1"/>
     <sheet name="BackUpList" sheetId="2" r:id="rId2"/>
+    <sheet name="BackUp(Cheap1)" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="44">
   <si>
     <t>ICs_List</t>
   </si>
@@ -138,13 +139,28 @@
     <t>LDO</t>
   </si>
   <si>
-    <t>MIC5209-3.3YS</t>
+    <t>TLV1117LV33DCYR</t>
   </si>
   <si>
     <t>TPS54540</t>
   </si>
   <si>
     <t>Buck</t>
+  </si>
+  <si>
+    <t>TPS54560DDAR</t>
+  </si>
+  <si>
+    <t>ICM-42605</t>
+  </si>
+  <si>
+    <t>BMP388</t>
+  </si>
+  <si>
+    <t>TotalPriceS1</t>
+  </si>
+  <si>
+    <t>ICM-42688-P (HXY)</t>
   </si>
 </sst>
 </file>
@@ -158,7 +174,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -167,7 +183,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="26"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -195,20 +210,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF6D727F"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF111111"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -339,12 +358,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -662,13 +687,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -677,37 +699,37 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -722,77 +744,86 @@
     <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -802,10 +833,67 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="8" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="6" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1353,223 +1441,465 @@
   </cols>
   <sheetData>
     <row r="2" ht="33.75" spans="1:18">
-      <c r="G2" s="1"/>
-      <c r="J2" s="1" t="s">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="3" t="s">
         <v>0</v>
       </c>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O3" t="s">
+      <c r="O3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P3" t="s">
+      <c r="P3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="Q3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="R3" t="s">
+      <c r="R3" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" ht="17.25" spans="1:18">
-      <c r="A4">
+      <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>1</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="4">
         <v>10.1703</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="5">
         <v>245</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="6">
         <f>E4*D4</f>
         <v>10.1703</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:18">
-      <c r="A5">
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+    </row>
+    <row r="5" ht="17.25" spans="1:18">
+      <c r="A5" s="2">
         <v>2</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:18">
-      <c r="A6">
+      <c r="E5" s="9">
+        <v>2.7743</v>
+      </c>
+      <c r="F5" s="10">
+        <v>121749</v>
+      </c>
+      <c r="G5" s="6">
+        <f t="shared" ref="G5:G13" si="0">E5*D5</f>
+        <v>2.7743</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+    </row>
+    <row r="6" ht="17.25" spans="1:18">
+      <c r="A6" s="2">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:18">
-      <c r="A7">
+      <c r="E6" s="9">
+        <v>14.9397</v>
+      </c>
+      <c r="F6" s="10">
+        <v>6540</v>
+      </c>
+      <c r="G6" s="6">
+        <f t="shared" si="0"/>
+        <v>29.8794</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+    </row>
+    <row r="7" s="22" customFormat="1" ht="17.25" spans="1:18">
+      <c r="A7" s="23">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="23">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="A8">
+      <c r="E7" s="24">
+        <v>0.0377</v>
+      </c>
+      <c r="F7" s="23">
+        <v>0</v>
+      </c>
+      <c r="G7" s="25">
+        <f t="shared" si="0"/>
+        <v>0.0377</v>
+      </c>
+      <c r="H7" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
+    </row>
+    <row r="8" ht="17.25" spans="1:18">
+      <c r="A8" s="2">
         <v>5</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9">
+      <c r="E8" s="9">
+        <v>1.3591</v>
+      </c>
+      <c r="F8" s="10">
+        <v>54901</v>
+      </c>
+      <c r="G8" s="6">
+        <f t="shared" si="0"/>
+        <v>1.3591</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+    </row>
+    <row r="9" ht="17.25" spans="1:18">
+      <c r="A9" s="2">
         <v>6</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="A10">
+      <c r="E9" s="9">
+        <v>2.0193</v>
+      </c>
+      <c r="F9" s="10">
+        <v>40888</v>
+      </c>
+      <c r="G9" s="6">
+        <f t="shared" si="0"/>
+        <v>2.0193</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+    </row>
+    <row r="10" ht="17.25" spans="1:18">
+      <c r="A10" s="2">
         <v>7</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11">
+      <c r="E10" s="9">
+        <v>0.1252</v>
+      </c>
+      <c r="F10" s="10">
+        <v>2051</v>
+      </c>
+      <c r="G10" s="6">
+        <f t="shared" si="0"/>
+        <v>0.1252</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+    </row>
+    <row r="11" ht="17.25" spans="1:18">
+      <c r="A11" s="2">
         <v>8</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:18">
-      <c r="A12">
+      <c r="E11" s="17">
+        <v>0.2025</v>
+      </c>
+      <c r="F11" s="18">
+        <v>20544</v>
+      </c>
+      <c r="G11" s="6">
+        <f t="shared" si="0"/>
+        <v>0.2025</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+    </row>
+    <row r="12" ht="17.25" spans="1:18">
+      <c r="A12" s="2">
         <v>9</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="A13">
+      <c r="E12" s="17">
+        <v>0.3597</v>
+      </c>
+      <c r="F12" s="18">
+        <v>2833</v>
+      </c>
+      <c r="G12" s="6">
+        <f t="shared" si="0"/>
+        <v>0.3597</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+    </row>
+    <row r="13" ht="17.25" spans="1:18">
+      <c r="A13" s="2">
         <v>10</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
         <v>2</v>
       </c>
+      <c r="E13" s="17">
+        <v>1.1085</v>
+      </c>
+      <c r="F13" s="19">
+        <v>51812</v>
+      </c>
+      <c r="G13" s="6">
+        <f t="shared" si="0"/>
+        <v>2.217</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H4" r:id="rId1" display="STM32H743VGT6_JLC"/>
+    <hyperlink ref="H13" r:id="rId2" display="TPS54560DDAR"/>
+    <hyperlink ref="H5" r:id="rId3" display="W25Q128JV"/>
+    <hyperlink ref="H6" r:id="rId4" display="ICM-42688-P"/>
+    <hyperlink ref="H7" r:id="rId5" display="SPL06"/>
+    <hyperlink ref="H8" r:id="rId6" display="TJA1051TK/3"/>
+    <hyperlink ref="H9" r:id="rId7" display="AT7456E"/>
+    <hyperlink ref="H10" r:id="rId8" display="SGM3001"/>
+    <hyperlink ref="H11" r:id="rId9" display="LP5907-3.3"/>
+    <hyperlink ref="H12" r:id="rId10" display="TLV1117LV33DCYR"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1579,9 +1909,996 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="18.2857142857143" customWidth="1"/>
+    <col min="3" max="3" width="16.4285714285714" customWidth="1"/>
+    <col min="4" max="4" width="18.7142857142857" customWidth="1"/>
+    <col min="5" max="5" width="16.8571428571429" customWidth="1"/>
+    <col min="6" max="6" width="27.1428571428571" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="25.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="16.8571428571429" customWidth="1"/>
+    <col min="10" max="10" width="27.1428571428571" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="25.7142857142857" customWidth="1"/>
+    <col min="13" max="13" width="16.8571428571429" customWidth="1"/>
+    <col min="14" max="14" width="27.1428571428571" customWidth="1"/>
+    <col min="15" max="15" width="24" customWidth="1"/>
+    <col min="16" max="16" width="25.7142857142857" customWidth="1"/>
+    <col min="17" max="17" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="33.75" spans="1:18">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" ht="17.25" spans="1:18">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4">
+        <v>10.1703</v>
+      </c>
+      <c r="F3" s="5">
+        <v>245</v>
+      </c>
+      <c r="G3" s="6">
+        <f t="shared" ref="G3:G12" si="0">E3*D3</f>
+        <v>10.1703</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+    </row>
+    <row r="4" ht="17.25" spans="1:18">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="9">
+        <v>2.7743</v>
+      </c>
+      <c r="F4" s="10">
+        <v>121749</v>
+      </c>
+      <c r="G4" s="6">
+        <f t="shared" si="0"/>
+        <v>2.7743</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+    </row>
+    <row r="5" ht="17.25" spans="1:18">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2</v>
+      </c>
+      <c r="E5" s="21">
+        <v>7.7108</v>
+      </c>
+      <c r="F5" s="10">
+        <v>6540</v>
+      </c>
+      <c r="G5" s="6">
+        <f t="shared" si="0"/>
+        <v>15.4216</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="17.25" spans="1:18">
+      <c r="A6" s="13">
+        <v>4</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="13">
+        <v>1</v>
+      </c>
+      <c r="E6" s="21">
+        <v>2.4771</v>
+      </c>
+      <c r="F6" s="14">
+        <v>14187</v>
+      </c>
+      <c r="G6" s="15">
+        <f t="shared" si="0"/>
+        <v>2.4771</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+    </row>
+    <row r="7" ht="17.25" spans="1:18">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="9">
+        <v>1.3591</v>
+      </c>
+      <c r="F7" s="10">
+        <v>54901</v>
+      </c>
+      <c r="G7" s="6">
+        <f t="shared" si="0"/>
+        <v>1.3591</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" ht="17.25" spans="1:18">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="9">
+        <v>2.0193</v>
+      </c>
+      <c r="F8" s="10">
+        <v>40888</v>
+      </c>
+      <c r="G8" s="6">
+        <f t="shared" si="0"/>
+        <v>2.0193</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+    </row>
+    <row r="9" ht="17.25" spans="1:18">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0.1252</v>
+      </c>
+      <c r="F9" s="10">
+        <v>2051</v>
+      </c>
+      <c r="G9" s="6">
+        <f t="shared" si="0"/>
+        <v>0.1252</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+    </row>
+    <row r="10" ht="17.25" spans="1:18">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="17">
+        <v>0.2025</v>
+      </c>
+      <c r="F10" s="18">
+        <v>20544</v>
+      </c>
+      <c r="G10" s="6">
+        <f t="shared" si="0"/>
+        <v>0.2025</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+    </row>
+    <row r="11" ht="17.25" spans="1:18">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="17">
+        <v>0.3597</v>
+      </c>
+      <c r="F11" s="18">
+        <v>2833</v>
+      </c>
+      <c r="G11" s="6">
+        <f t="shared" si="0"/>
+        <v>0.3597</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+    </row>
+    <row r="12" ht="17.25" spans="1:18">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="2">
+        <v>2</v>
+      </c>
+      <c r="E12" s="17">
+        <v>1.1085</v>
+      </c>
+      <c r="F12" s="19">
+        <v>51812</v>
+      </c>
+      <c r="G12" s="6">
+        <f t="shared" si="0"/>
+        <v>2.217</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="F13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="20">
+        <f>SUM(G3:G12)</f>
+        <v>37.1261</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H3" r:id="rId1" display="STM32H743VGT6_JLC"/>
+    <hyperlink ref="H4" r:id="rId2" display="W25Q128JV"/>
+    <hyperlink ref="H6" r:id="rId3" display="BMP388"/>
+    <hyperlink ref="H5" r:id="rId4" display="ICM-42605"/>
+    <hyperlink ref="H12" r:id="rId5" display="TPS54560DDAR"/>
+    <hyperlink ref="H7" r:id="rId6" display="TJA1051TK/3"/>
+    <hyperlink ref="H8" r:id="rId7" display="AT7456E"/>
+    <hyperlink ref="H9" r:id="rId8" display="SGM3001"/>
+    <hyperlink ref="H10" r:id="rId9" display="LP5907-3.3"/>
+    <hyperlink ref="H11" r:id="rId10" display="TLV1117LV33DCYR"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:R13"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="18.2857142857143" customWidth="1"/>
+    <col min="3" max="3" width="16.4285714285714" customWidth="1"/>
+    <col min="4" max="4" width="18.7142857142857" customWidth="1"/>
+    <col min="5" max="5" width="16.8571428571429" customWidth="1"/>
+    <col min="6" max="6" width="27.1428571428571" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="25.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="16.8571428571429" customWidth="1"/>
+    <col min="10" max="10" width="27.1428571428571" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="25.7142857142857" customWidth="1"/>
+    <col min="13" max="13" width="16.8571428571429" customWidth="1"/>
+    <col min="14" max="14" width="27.1428571428571" customWidth="1"/>
+    <col min="15" max="15" width="24" customWidth="1"/>
+    <col min="16" max="16" width="25.7142857142857" customWidth="1"/>
+    <col min="17" max="17" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="33.75" spans="1:18">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" ht="17.25" spans="1:18">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4">
+        <v>10.1703</v>
+      </c>
+      <c r="F3" s="5">
+        <v>245</v>
+      </c>
+      <c r="G3" s="6">
+        <f t="shared" ref="G3:G12" si="0">E3*D3</f>
+        <v>10.1703</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+    </row>
+    <row r="4" ht="17.25" spans="1:18">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="9">
+        <v>2.7743</v>
+      </c>
+      <c r="F4" s="10">
+        <v>121749</v>
+      </c>
+      <c r="G4" s="6">
+        <f t="shared" si="0"/>
+        <v>2.7743</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+    </row>
+    <row r="5" ht="17.25" spans="1:18">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2</v>
+      </c>
+      <c r="E5" s="12">
+        <v>3.5085</v>
+      </c>
+      <c r="F5" s="10">
+        <v>6540</v>
+      </c>
+      <c r="G5" s="6">
+        <f t="shared" si="0"/>
+        <v>7.017</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="17.25" spans="1:18">
+      <c r="A6" s="13">
+        <v>4</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="13">
+        <v>1</v>
+      </c>
+      <c r="E6" s="12">
+        <v>1.539</v>
+      </c>
+      <c r="F6" s="14">
+        <v>14187</v>
+      </c>
+      <c r="G6" s="15">
+        <f t="shared" si="0"/>
+        <v>1.539</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+    </row>
+    <row r="7" ht="17.25" spans="1:18">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="9">
+        <v>1.3591</v>
+      </c>
+      <c r="F7" s="10">
+        <v>54901</v>
+      </c>
+      <c r="G7" s="6">
+        <f t="shared" si="0"/>
+        <v>1.3591</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" ht="17.25" spans="1:18">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="9">
+        <v>2.0193</v>
+      </c>
+      <c r="F8" s="10">
+        <v>40888</v>
+      </c>
+      <c r="G8" s="6">
+        <f t="shared" si="0"/>
+        <v>2.0193</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+    </row>
+    <row r="9" ht="17.25" spans="1:18">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0.1252</v>
+      </c>
+      <c r="F9" s="10">
+        <v>2051</v>
+      </c>
+      <c r="G9" s="6">
+        <f t="shared" si="0"/>
+        <v>0.1252</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+    </row>
+    <row r="10" ht="17.25" spans="1:18">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="17">
+        <v>0.2025</v>
+      </c>
+      <c r="F10" s="18">
+        <v>20544</v>
+      </c>
+      <c r="G10" s="6">
+        <f t="shared" si="0"/>
+        <v>0.2025</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+    </row>
+    <row r="11" ht="17.25" spans="1:18">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="17">
+        <v>0.3597</v>
+      </c>
+      <c r="F11" s="18">
+        <v>2833</v>
+      </c>
+      <c r="G11" s="6">
+        <f t="shared" si="0"/>
+        <v>0.3597</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+    </row>
+    <row r="12" ht="17.25" spans="1:18">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="2">
+        <v>2</v>
+      </c>
+      <c r="E12" s="17">
+        <v>1.1085</v>
+      </c>
+      <c r="F12" s="19">
+        <v>51812</v>
+      </c>
+      <c r="G12" s="6">
+        <f t="shared" si="0"/>
+        <v>2.217</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+    </row>
+    <row r="13" customFormat="1" spans="1:18">
+      <c r="F13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="20">
+        <f>SUM(G3:G12)</f>
+        <v>27.7834</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H3" r:id="rId1" display="STM32H743VGT6_JLC"/>
+    <hyperlink ref="H4" r:id="rId2" display="W25Q128JV"/>
+    <hyperlink ref="H6" r:id="rId3" display="BMP388"/>
+    <hyperlink ref="H12" r:id="rId4" display="TPS54560DDAR"/>
+    <hyperlink ref="H7" r:id="rId5" display="TJA1051TK/3"/>
+    <hyperlink ref="H8" r:id="rId6" display="AT7456E"/>
+    <hyperlink ref="H9" r:id="rId7" display="SGM3001"/>
+    <hyperlink ref="H10" r:id="rId8" display="LP5907-3.3"/>
+    <hyperlink ref="H11" r:id="rId9" display="TLV1117LV33DCYR"/>
+    <hyperlink ref="H5" r:id="rId10" display="ICM-42688-P"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/FlyControl/Components/ICs_List/ICs_List.xlsx
+++ b/FlyControl/Components/ICs_List/ICs_List.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11580" activeTab="2"/>
+    <workbookView windowWidth="22590" windowHeight="11580"/>
   </bookViews>
   <sheets>
     <sheet name="OriginList" sheetId="1" r:id="rId1"/>
@@ -204,7 +204,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -212,7 +212,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -684,12 +684,12 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -814,7 +814,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -839,34 +839,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="8" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
@@ -875,12 +860,12 @@
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -893,7 +878,7 @@
     <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="6" applyFill="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1541,7 +1526,7 @@
         <f>E4*D4</f>
         <v>10.1703</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="15" t="s">
         <v>21</v>
       </c>
       <c r="I4" s="2"/>
@@ -1559,7 +1544,7 @@
       <c r="A5" s="2">
         <v>2</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -1568,17 +1553,17 @@
       <c r="D5" s="2">
         <v>1</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <v>2.7743</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="5">
         <v>121749</v>
       </c>
       <c r="G5" s="6">
         <f t="shared" ref="G5:G13" si="0">E5*D5</f>
         <v>2.7743</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="12" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="2"/>
@@ -1605,17 +1590,17 @@
       <c r="D6" s="2">
         <v>2</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="8">
         <v>14.9397</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="5">
         <v>6540</v>
       </c>
       <c r="G6" s="6">
         <f t="shared" si="0"/>
         <v>29.8794</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="7" t="s">
         <v>24</v>
       </c>
       <c r="I6" s="2"/>
@@ -1629,42 +1614,42 @@
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
     </row>
-    <row r="7" s="22" customFormat="1" ht="17.25" spans="1:18">
-      <c r="A7" s="23">
+    <row r="7" s="17" customFormat="1" ht="17.25" spans="1:18">
+      <c r="A7" s="18">
         <v>4</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="23">
-        <v>1</v>
-      </c>
-      <c r="E7" s="24">
+      <c r="D7" s="18">
+        <v>1</v>
+      </c>
+      <c r="E7" s="19">
         <v>0.0377</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="18">
         <v>0</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="20">
         <f t="shared" si="0"/>
         <v>0.0377</v>
       </c>
-      <c r="H7" s="26" t="s">
+      <c r="H7" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="18"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="18"/>
+      <c r="Q7" s="18"/>
+      <c r="R7" s="18"/>
     </row>
     <row r="8" ht="17.25" spans="1:18">
       <c r="A8" s="2">
@@ -1679,17 +1664,17 @@
       <c r="D8" s="2">
         <v>1</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="8">
         <v>1.3591</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="5">
         <v>54901</v>
       </c>
       <c r="G8" s="6">
         <f t="shared" si="0"/>
         <v>1.3591</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I8" s="2"/>
@@ -1716,17 +1701,17 @@
       <c r="D9" s="2">
         <v>1</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="8">
         <v>2.0193</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="5">
         <v>40888</v>
       </c>
       <c r="G9" s="6">
         <f t="shared" si="0"/>
         <v>2.0193</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="7" t="s">
         <v>30</v>
       </c>
       <c r="I9" s="2"/>
@@ -1753,17 +1738,17 @@
       <c r="D10" s="2">
         <v>1</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="8">
         <v>0.1252</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="5">
         <v>2051</v>
       </c>
       <c r="G10" s="6">
         <f t="shared" si="0"/>
         <v>0.1252</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I10" s="2"/>
@@ -1781,7 +1766,7 @@
       <c r="A11" s="2">
         <v>8</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -1790,17 +1775,17 @@
       <c r="D11" s="2">
         <v>1</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="4">
         <v>0.2025</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="13">
         <v>20544</v>
       </c>
       <c r="G11" s="6">
         <f t="shared" si="0"/>
         <v>0.2025</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="7" t="s">
         <v>34</v>
       </c>
       <c r="I11" s="2"/>
@@ -1827,17 +1812,17 @@
       <c r="D12" s="2">
         <v>1</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="4">
         <v>0.3597</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="13">
         <v>2833</v>
       </c>
       <c r="G12" s="6">
         <f t="shared" si="0"/>
         <v>0.3597</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="7" t="s">
         <v>36</v>
       </c>
       <c r="I12" s="2"/>
@@ -1864,10 +1849,10 @@
       <c r="D13" s="2">
         <v>2</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="4">
         <v>1.1085</v>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="14">
         <v>51812</v>
       </c>
       <c r="G13" s="6">
@@ -2031,7 +2016,7 @@
         <f t="shared" ref="G3:G12" si="0">E3*D3</f>
         <v>10.1703</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="15" t="s">
         <v>21</v>
       </c>
       <c r="I3" s="2"/>
@@ -2049,7 +2034,7 @@
       <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -2058,17 +2043,17 @@
       <c r="D4" s="2">
         <v>1</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="8">
         <v>2.7743</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="5">
         <v>121749</v>
       </c>
       <c r="G4" s="6">
         <f t="shared" si="0"/>
         <v>2.7743</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="12" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="2"/>
@@ -2095,17 +2080,17 @@
       <c r="D5" s="2">
         <v>2</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="4">
         <v>7.7108</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="5">
         <v>6540</v>
       </c>
       <c r="G5" s="6">
         <f t="shared" si="0"/>
         <v>15.4216</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I5" s="2"/>
@@ -2120,41 +2105,41 @@
       <c r="R5" s="2"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="17.25" spans="1:18">
-      <c r="A6" s="13">
+      <c r="A6" s="9">
         <v>4</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="13">
-        <v>1</v>
-      </c>
-      <c r="E6" s="21">
+      <c r="D6" s="9">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4">
         <v>2.4771</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="5">
         <v>14187</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="10">
         <f t="shared" si="0"/>
         <v>2.4771</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
     </row>
     <row r="7" ht="17.25" spans="1:18">
       <c r="A7" s="2">
@@ -2169,17 +2154,17 @@
       <c r="D7" s="2">
         <v>1</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="8">
         <v>1.3591</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="5">
         <v>54901</v>
       </c>
       <c r="G7" s="6">
         <f t="shared" si="0"/>
         <v>1.3591</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="12" t="s">
         <v>28</v>
       </c>
       <c r="I7" s="2"/>
@@ -2206,17 +2191,17 @@
       <c r="D8" s="2">
         <v>1</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="8">
         <v>2.0193</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="5">
         <v>40888</v>
       </c>
       <c r="G8" s="6">
         <f t="shared" si="0"/>
         <v>2.0193</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="12" t="s">
         <v>30</v>
       </c>
       <c r="I8" s="2"/>
@@ -2243,17 +2228,17 @@
       <c r="D9" s="2">
         <v>1</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="8">
         <v>0.1252</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="5">
         <v>2051</v>
       </c>
       <c r="G9" s="6">
         <f t="shared" si="0"/>
         <v>0.1252</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="12" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="2"/>
@@ -2271,7 +2256,7 @@
       <c r="A10" s="2">
         <v>8</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -2280,17 +2265,17 @@
       <c r="D10" s="2">
         <v>1</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="4">
         <v>0.2025</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="13">
         <v>20544</v>
       </c>
       <c r="G10" s="6">
         <f t="shared" si="0"/>
         <v>0.2025</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="12" t="s">
         <v>34</v>
       </c>
       <c r="I10" s="2"/>
@@ -2317,17 +2302,17 @@
       <c r="D11" s="2">
         <v>1</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="4">
         <v>0.3597</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="13">
         <v>2833</v>
       </c>
       <c r="G11" s="6">
         <f t="shared" si="0"/>
         <v>0.3597</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="12" t="s">
         <v>36</v>
       </c>
       <c r="I11" s="2"/>
@@ -2354,17 +2339,17 @@
       <c r="D12" s="2">
         <v>2</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="4">
         <v>1.1085</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="14">
         <v>51812</v>
       </c>
       <c r="G12" s="6">
         <f t="shared" si="0"/>
         <v>2.217</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="15" t="s">
         <v>39</v>
       </c>
       <c r="I12" s="2"/>
@@ -2382,7 +2367,7 @@
       <c r="F13" t="s">
         <v>42</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="16">
         <f>SUM(G3:G12)</f>
         <v>37.1261</v>
       </c>
@@ -2548,7 +2533,7 @@
       <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -2557,17 +2542,17 @@
       <c r="D4" s="2">
         <v>1</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="8">
         <v>2.7743</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="5">
         <v>121749</v>
       </c>
       <c r="G4" s="6">
         <f t="shared" si="0"/>
         <v>2.7743</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="7" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="2"/>
@@ -2594,17 +2579,17 @@
       <c r="D5" s="2">
         <v>2</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="8">
         <v>3.5085</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="5">
         <v>6540</v>
       </c>
       <c r="G5" s="6">
         <f t="shared" si="0"/>
         <v>7.017</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="7" t="s">
         <v>24</v>
       </c>
       <c r="I5" s="2"/>
@@ -2619,41 +2604,41 @@
       <c r="R5" s="2"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="17.25" spans="1:18">
-      <c r="A6" s="13">
+      <c r="A6" s="9">
         <v>4</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="13">
-        <v>1</v>
-      </c>
-      <c r="E6" s="12">
+      <c r="D6" s="9">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8">
         <v>1.539</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="5">
         <v>14187</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="10">
         <f t="shared" si="0"/>
         <v>1.539</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
     </row>
     <row r="7" ht="17.25" spans="1:18">
       <c r="A7" s="2">
@@ -2668,17 +2653,17 @@
       <c r="D7" s="2">
         <v>1</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="8">
         <v>1.3591</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="5">
         <v>54901</v>
       </c>
       <c r="G7" s="6">
         <f t="shared" si="0"/>
         <v>1.3591</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I7" s="2"/>
@@ -2705,17 +2690,17 @@
       <c r="D8" s="2">
         <v>1</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="8">
         <v>2.0193</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="5">
         <v>40888</v>
       </c>
       <c r="G8" s="6">
         <f t="shared" si="0"/>
         <v>2.0193</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="12" t="s">
         <v>30</v>
       </c>
       <c r="I8" s="2"/>
@@ -2742,17 +2727,17 @@
       <c r="D9" s="2">
         <v>1</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="8">
         <v>0.1252</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="5">
         <v>2051</v>
       </c>
       <c r="G9" s="6">
         <f t="shared" si="0"/>
         <v>0.1252</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="12" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="2"/>
@@ -2770,7 +2755,7 @@
       <c r="A10" s="2">
         <v>8</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -2779,17 +2764,17 @@
       <c r="D10" s="2">
         <v>1</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="4">
         <v>0.2025</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="13">
         <v>20544</v>
       </c>
       <c r="G10" s="6">
         <f t="shared" si="0"/>
         <v>0.2025</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="12" t="s">
         <v>34</v>
       </c>
       <c r="I10" s="2"/>
@@ -2816,17 +2801,17 @@
       <c r="D11" s="2">
         <v>1</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="4">
         <v>0.3597</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="13">
         <v>2833</v>
       </c>
       <c r="G11" s="6">
         <f t="shared" si="0"/>
         <v>0.3597</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="12" t="s">
         <v>36</v>
       </c>
       <c r="I11" s="2"/>
@@ -2853,17 +2838,17 @@
       <c r="D12" s="2">
         <v>2</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="4">
         <v>1.1085</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="14">
         <v>51812</v>
       </c>
       <c r="G12" s="6">
         <f t="shared" si="0"/>
         <v>2.217</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="15" t="s">
         <v>39</v>
       </c>
       <c r="I12" s="2"/>
@@ -2881,7 +2866,7 @@
       <c r="F13" t="s">
         <v>42</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="16">
         <f>SUM(G3:G12)</f>
         <v>27.7834</v>
       </c>
